--- a/results/random_forest/neighborhood_error_report.xlsx
+++ b/results/random_forest/neighborhood_error_report.xlsx
@@ -458,16 +458,16 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>28036.935</v>
+        <v>27818.34251305729</v>
       </c>
       <c r="D2" t="n">
-        <v>32922.23273419499</v>
+        <v>32766.47975219715</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4324447393314718</v>
+        <v>0.4378021718821604</v>
       </c>
       <c r="F2" t="n">
-        <v>50.94334022465242</v>
+        <v>50.55986926028597</v>
       </c>
     </row>
     <row r="3">
@@ -480,16 +480,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>18477.51625</v>
+        <v>17213.19815713311</v>
       </c>
       <c r="D3" t="n">
-        <v>23641.56518857968</v>
+        <v>22159.33657294347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7987842112205443</v>
+        <v>0.8232240775617423</v>
       </c>
       <c r="F3" t="n">
-        <v>16.09299171476918</v>
+        <v>15.2359284668518</v>
       </c>
     </row>
     <row r="4">
@@ -502,16 +502,16 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>34292.776</v>
+        <v>35170.6540566517</v>
       </c>
       <c r="D4" t="n">
-        <v>39827.93101334438</v>
+        <v>42617.69159147805</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4960047373804992</v>
+        <v>-0.7129209492053625</v>
       </c>
       <c r="F4" t="n">
-        <v>14.30056174452485</v>
+        <v>14.40287090626631</v>
       </c>
     </row>
     <row r="5">
@@ -524,104 +524,104 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>13584.09333333333</v>
+        <v>13240.4821794812</v>
       </c>
       <c r="D5" t="n">
-        <v>20107.77501682173</v>
+        <v>19787.35386610084</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2673307068395897</v>
+        <v>0.2904951040717358</v>
       </c>
       <c r="F5" t="n">
-        <v>13.42311361598471</v>
+        <v>13.08004504097461</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NPkVill</t>
+          <t>MeadowV</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14882.92</v>
+        <v>10669.66390083643</v>
       </c>
       <c r="D6" t="n">
-        <v>15032.81535463001</v>
+        <v>13148.66410533953</v>
       </c>
       <c r="E6" t="n">
-        <v>-3614.768599782398</v>
+        <v>0.6047002092680125</v>
       </c>
       <c r="F6" t="n">
-        <v>11.65332371323529</v>
+        <v>11.65667100426233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MeadowV</t>
+          <t>NPkVill</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>10543.26</v>
+        <v>14689.71202354309</v>
       </c>
       <c r="D7" t="n">
-        <v>12850.88681719514</v>
+        <v>14799.03249554929</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6224021441759331</v>
+        <v>-3503.181804869183</v>
       </c>
       <c r="F7" t="n">
-        <v>11.55110622530586</v>
+        <v>11.50159055925172</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NridgHt</t>
+          <t>OldTown</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>40901.68235294117</v>
+        <v>10612.33242615162</v>
       </c>
       <c r="D8" t="n">
-        <v>55554.23991272132</v>
+        <v>15408.72117640304</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5818354859641259</v>
+        <v>0.9062308386445647</v>
       </c>
       <c r="F8" t="n">
-        <v>11.52977986383873</v>
+        <v>10.98543393338925</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OldTown</t>
+          <t>NridgHt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>11016.42052631579</v>
+        <v>37737.24839854953</v>
       </c>
       <c r="D9" t="n">
-        <v>15376.45681228577</v>
+        <v>52350.43160212087</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9066231145357475</v>
+        <v>0.6286757706393337</v>
       </c>
       <c r="F9" t="n">
-        <v>11.05496828212708</v>
+        <v>10.90177956620879</v>
       </c>
     </row>
     <row r="10">
@@ -634,148 +634,148 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>26173.35333333333</v>
+        <v>25746.45671941385</v>
       </c>
       <c r="D10" t="n">
-        <v>27858.82295862839</v>
+        <v>26919.2939390147</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1233920600719</v>
+        <v>-2.849961910021052</v>
       </c>
       <c r="F10" t="n">
-        <v>10.98013607375843</v>
+        <v>10.84143182990892</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SWISU</t>
+          <t>BrkSide</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
-        <v>16346.7025</v>
+        <v>10999.32237495189</v>
       </c>
       <c r="D11" t="n">
-        <v>18448.29703224189</v>
+        <v>15378.14086928626</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1688897108917584</v>
+        <v>0.5259082341076595</v>
       </c>
       <c r="F11" t="n">
-        <v>10.58433877882452</v>
+        <v>10.71845580165202</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BrkSide</t>
+          <t>Blmngtn</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>10538.14571428572</v>
+        <v>21863.04899851792</v>
       </c>
       <c r="D12" t="n">
-        <v>15105.2866776191</v>
+        <v>27653.20088285786</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5425825939658788</v>
+        <v>-0.1149863970829526</v>
       </c>
       <c r="F12" t="n">
-        <v>10.34009690110286</v>
+        <v>9.136239990669811</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NoRidge</t>
+          <t>SWISU</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>28845.74166666666</v>
+        <v>14079.63220628617</v>
       </c>
       <c r="D13" t="n">
-        <v>37231.94584619301</v>
+        <v>16696.8353656001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4125366048196711</v>
+        <v>0.3192080311942508</v>
       </c>
       <c r="F13" t="n">
-        <v>8.866581790476397</v>
+        <v>8.953814399446529</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Blmngtn</t>
+          <t>StoneBr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>21446.13</v>
+        <v>23749.81476575859</v>
       </c>
       <c r="D14" t="n">
-        <v>28575.00648015675</v>
+        <v>27735.52656092406</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.190560383393191</v>
+        <v>0.9129570952949424</v>
       </c>
       <c r="F14" t="n">
-        <v>8.837641180618579</v>
+        <v>8.85519174621402</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BrDale</t>
+          <t>NoRidge</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>10408.23</v>
+        <v>25687.16470805452</v>
       </c>
       <c r="D15" t="n">
-        <v>11552.67469530325</v>
+        <v>32450.40216188087</v>
       </c>
       <c r="E15" t="n">
-        <v>-37.13265503300001</v>
+        <v>0.5537384091816064</v>
       </c>
       <c r="F15" t="n">
-        <v>8.733097977419463</v>
+        <v>8.02889292503821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>StoneBr</t>
+          <t>BrDale</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>22850.2825</v>
+        <v>9280.102546549582</v>
       </c>
       <c r="D16" t="n">
-        <v>26065.60282136162</v>
+        <v>9944.344086487119</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9231230594874863</v>
+        <v>-27.2542798029861</v>
       </c>
       <c r="F16" t="n">
-        <v>8.540632678445085</v>
+        <v>7.769774996628656</v>
       </c>
     </row>
     <row r="17">
@@ -788,16 +788,16 @@
         <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>13521.04833333333</v>
+        <v>12902.52407744931</v>
       </c>
       <c r="D17" t="n">
-        <v>14131.90750479389</v>
+        <v>13693.87725836939</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9219149296535409</v>
+        <v>0.9266805336890375</v>
       </c>
       <c r="F17" t="n">
-        <v>7.982496038882175</v>
+        <v>7.738411854391926</v>
       </c>
     </row>
     <row r="18">
@@ -810,60 +810,60 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>14520.61636363636</v>
+        <v>13954.8548468412</v>
       </c>
       <c r="D18" t="n">
-        <v>19590.44127898047</v>
+        <v>18263.6015426766</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7117175747360589</v>
+        <v>0.749445286727342</v>
       </c>
       <c r="F18" t="n">
-        <v>7.683909301033411</v>
+        <v>7.450027285621776</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Somerst</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>16875.99230769231</v>
+        <v>17733.53407146205</v>
       </c>
       <c r="D19" t="n">
-        <v>21820.05438883372</v>
+        <v>25136.87017302718</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7818095501042833</v>
+        <v>0.7301758524320971</v>
       </c>
       <c r="F19" t="n">
-        <v>7.241914828722958</v>
+        <v>7.216784384735029</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CollgCr</t>
+          <t>Somerst</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
-        <v>13510.21</v>
+        <v>16445.79289033152</v>
       </c>
       <c r="D20" t="n">
-        <v>19648.34993798875</v>
+        <v>21420.24475401915</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7455300208942769</v>
+        <v>0.7897321190223082</v>
       </c>
       <c r="F20" t="n">
-        <v>7.106399505530645</v>
+        <v>6.974672784644836</v>
       </c>
     </row>
     <row r="21">
@@ -876,38 +876,38 @@
         <v>11</v>
       </c>
       <c r="C21" t="n">
-        <v>16555.79</v>
+        <v>16107.73333621361</v>
       </c>
       <c r="D21" t="n">
-        <v>22587.23073624785</v>
+        <v>21964.8528904406</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6682227978301388</v>
+        <v>0.686254748431476</v>
       </c>
       <c r="F21" t="n">
-        <v>7.077165984774078</v>
+        <v>6.901684279673206</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>CollgCr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>15884.81714285715</v>
+        <v>12724.81468175121</v>
       </c>
       <c r="D22" t="n">
-        <v>22608.62197355438</v>
+        <v>18392.08246764945</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7817236946365035</v>
+        <v>0.7770301217820913</v>
       </c>
       <c r="F22" t="n">
-        <v>6.491575458869081</v>
+        <v>6.773199233978566</v>
       </c>
     </row>
     <row r="23">
@@ -920,60 +920,60 @@
         <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>8900.696896551724</v>
+        <v>8107.867415434001</v>
       </c>
       <c r="D23" t="n">
-        <v>12952.26487019016</v>
+        <v>11863.25384717098</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8448324498910423</v>
+        <v>0.8698281383206111</v>
       </c>
       <c r="F23" t="n">
-        <v>5.652675048824323</v>
+        <v>5.196834939754409</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Veenker</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>12431.14</v>
+        <v>6543.75818776199</v>
       </c>
       <c r="D24" t="n">
-        <v>16632.01154374299</v>
+        <v>10232.41953690936</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8996376206834649</v>
+        <v>0.720782484866159</v>
       </c>
       <c r="F24" t="n">
-        <v>4.766950168350167</v>
+        <v>4.005644348135315</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Veenker</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>7519.009375000003</v>
+        <v>9411.032110831351</v>
       </c>
       <c r="D25" t="n">
-        <v>11092.55566281589</v>
+        <v>13061.70359804285</v>
       </c>
       <c r="E25" t="n">
-        <v>0.671867524651404</v>
+        <v>0.9381013692941041</v>
       </c>
       <c r="F25" t="n">
-        <v>4.570411513146897</v>
+        <v>3.527214719519461</v>
       </c>
     </row>
   </sheetData>
